--- a/master_parts_list.xlsx
+++ b/master_parts_list.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewhoffman/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BAE07716-D2C0-3646-98A7-A02CFFE5391B}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67C59CA3-9F44-A84B-9547-B0E6A9CCE8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6560" yWindow="8560" windowWidth="37220" windowHeight="15040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1440" yWindow="3040" windowWidth="23360" windowHeight="15040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="128">
   <si>
     <t>Total</t>
   </si>
@@ -69,9 +74,6 @@
     <t>Used in Sections</t>
   </si>
   <si>
-    <t>Body</t>
-  </si>
-  <si>
     <t>Differential Pivot, Wheel Assembly</t>
   </si>
   <si>
@@ -93,9 +95,6 @@
     <t>Battery Volt Meter</t>
   </si>
   <si>
-    <t>E15</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/DROK-Multimeter-6-5-100V-Backlight-Measuring/dp/B017FSED9I</t>
   </si>
   <si>
@@ -120,21 +119,6 @@
     <t>https://www.digikey.com/products/en?keywords=CN538B-50-ND</t>
   </si>
   <si>
-    <t>ServoCity</t>
-  </si>
-  <si>
-    <t>9” x 12” Aluminum Plate</t>
-  </si>
-  <si>
-    <t>S35</t>
-  </si>
-  <si>
-    <t>https://www.servocity.com/9-x-12-aluminum-pattern-plate</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Loctite-Marine-0-85-Fluid-Syringe-1405604/dp/B00KH62K50</t>
-  </si>
-  <si>
     <t>Allen Key Set</t>
   </si>
   <si>
@@ -210,96 +194,12 @@
     <t>D10</t>
   </si>
   <si>
-    <t>Authors: Andrew Hoffman and Knut Christianson (University of Washington)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The cost information contained in this document is of a budgetary and planning nature and is intended for informational purposes only.  It does not constitute a commitment on the part of the University of Washington </t>
-  </si>
-  <si>
-    <t>© 2018 University of Washington. Quaternary Research Center sponsorship acknowledged</t>
-  </si>
-  <si>
-    <t>Rasberry Pi 3 Model B</t>
-  </si>
-  <si>
-    <t>raspery Pi</t>
-  </si>
-  <si>
     <t>amazon</t>
   </si>
   <si>
-    <t>https://www.alliedelec.com/product/raspberry-pi/raspberry-pi-b-/70377493/?gclid=EAIaIQobChMIjIOZ3_av4QIVxR-tBh2vgAHmEAQYAyABEgLMgfD_BwE&amp;gclsrc=aw.ds</t>
-  </si>
-  <si>
-    <t>Allied devices</t>
-  </si>
-  <si>
-    <t>MSP32 Geared Motor</t>
-  </si>
-  <si>
-    <t>ElectroCraft</t>
-  </si>
-  <si>
-    <t>MobilPower Series</t>
-  </si>
-  <si>
-    <t>https://www.electrocraft.com/products/gearmotors/MPS32/</t>
-  </si>
-  <si>
-    <t>Motors</t>
-  </si>
-  <si>
-    <t>A123</t>
-  </si>
-  <si>
-    <t>A123 systems</t>
-  </si>
-  <si>
-    <t>http://www.a123systems.com/automotive/products/cells/</t>
-  </si>
-  <si>
-    <t>Hoyi vertical axis wind turbine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">v-air </t>
-  </si>
-  <si>
-    <t>tires</t>
-  </si>
-  <si>
-    <t>Monstor scooter parts</t>
-  </si>
-  <si>
-    <t>epoxy (loctite</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Premium-18x6-50-8-4Ply-Snow-Tire/dp/B00KIXBNGE/ref=sxbs_sxwds-stvp?keywords=atv+tires+snow+hog&amp;pd_rd_i=B00KIXBNGE&amp;pd_rd_r=95305df8-babb-497c-b0aa-33b662fc91ce&amp;pd_rd_w=5G197&amp;pd_rd_wg=5lnRt&amp;pf_rd_p=5c5ea0d7-2437-4d8a-88a7-ea6f32aeac11&amp;pf_rd_r=7KE5EJW6SSA22ESB93GE&amp;qid=1554171902&amp;s=gateway</t>
-  </si>
-  <si>
     <t>ublox</t>
   </si>
   <si>
-    <t>GPS module</t>
-  </si>
-  <si>
-    <t>https://www.u-blox.com/en/product/u-connect</t>
-  </si>
-  <si>
-    <t>http://www.raveon.com/rv_m7_ce.html</t>
-  </si>
-  <si>
-    <t>UHF radio modem</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Waveshare-Raspberry-Camera-Version-Raspberry-pi/dp/B00N9YWI1I/ref=redir_mobile_desktop?_encoding=UTF8&amp;dpID=41XRujO23BL&amp;dpPl=1&amp;keywords=Stereo%20camera&amp;pi=AC_SX236_SY340_FMwebp_QL65&amp;qid=1496382876&amp;ref=plSrch&amp;ref_=mp_s_a_1_6&amp;sr=8-6</t>
-  </si>
-  <si>
-    <t>waveshare rasberry pi camera module</t>
-  </si>
-  <si>
-    <t>stero camera</t>
-  </si>
-  <si>
     <t>wire braid</t>
   </si>
   <si>
@@ -316,6 +216,210 @@
   </si>
   <si>
     <t>wire 20 gauge black</t>
+  </si>
+  <si>
+    <t>MTT</t>
+  </si>
+  <si>
+    <t>Mechanical Build</t>
+  </si>
+  <si>
+    <t>MTT drive systems</t>
+  </si>
+  <si>
+    <t>Jetson nano</t>
+  </si>
+  <si>
+    <t>NVIDIA jetson nano</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>ublox reciever</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>LiDAR</t>
+  </si>
+  <si>
+    <t>I1</t>
+  </si>
+  <si>
+    <t>I2</t>
+  </si>
+  <si>
+    <t>Authors: Andrew Hoffman (Rice University, Lamont-Doherty Earth Observatory), Racheet Matai (Lamont Doherty Earth Observatory)</t>
+  </si>
+  <si>
+    <t>MTT articulated hinge system</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>MTT instrument sled</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>MTT 154</t>
+  </si>
+  <si>
+    <t>CAN BUS module</t>
+  </si>
+  <si>
+    <t>Deutsch DT 6-pin connectors</t>
+  </si>
+  <si>
+    <t>DC 10V-60V step down to 5V 5A</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>E5</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>Motor fuse relay switch power with harness</t>
+  </si>
+  <si>
+    <t>uxcell</t>
+  </si>
+  <si>
+    <t>ybbott</t>
+  </si>
+  <si>
+    <t>WWZMDiB</t>
+  </si>
+  <si>
+    <t>Deutusacc</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B09V7VZX47?ref=cm_sw_r_cso_cp_apan_dp_RDND0SMWS70R33E1QHFM&amp;ref_=cm_sw_r_cso_cp_apan_dp_RDND0SMWS70R33E1QHFM&amp;social_share=cm_sw_r_cso_cp_apan_dp_RDND0SMWS70R33E1QHFM&amp;titleSource=true&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0BVH43P9L?ref=cm_sw_r_cso_cp_apan_dp_AVSQJ4KQB05QJJ9VG0XK&amp;ref_=cm_sw_r_cso_cp_apan_dp_AVSQJ4KQB05QJJ9VG0XK&amp;social_share=cm_sw_r_cso_cp_apan_dp_AVSQJ4KQB05QJJ9VG0XK&amp;titleSource=true</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B07QRPFT96?ref=cm_sw_r_cso_cp_apan_dp_68QJJMF2A6TMFT4KS7R3&amp;ref_=cm_sw_r_cso_cp_apan_dp_68QJJMF2A6TMFT4KS7R3&amp;social_share=cm_sw_r_cso_cp_apan_dp_68QJJMF2A6TMFT4KS7R3&amp;titleSource=true&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/dp/B0CZDMJNVQ?ref=cm_sw_r_cso_cp_apan_dp_EZC62DH6YR9YAT762RDW&amp;ref_=cm_sw_r_cso_cp_apan_dp_EZC62DH6YR9YAT762RDW&amp;social_share=cm_sw_r_cso_cp_apan_dp_EZC62DH6YR9YAT762RDW&amp;titleSource=true&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.sparkfun.com/nvidia-jetson-orin-nano-developer-kit.html?gad_source=1&amp;gad_campaignid=17479024030&amp;gbraid=0AAAAADsj4ESZo4z6J-lZi4oH-Gbee1tDp&amp;gclid=CjwKCAjwpOfHBhAxEiwAm1SwEnDoAGNxGVBrMfDz3SxEgmrdc__G0zASww3opdL0DVLWkP3HYTavCRoCUl0QAvD_BwE</t>
+  </si>
+  <si>
+    <t>I3</t>
+  </si>
+  <si>
+    <t>I4</t>
+  </si>
+  <si>
+    <t>sparkfun</t>
+  </si>
+  <si>
+    <t>https://mtt136.com/</t>
+  </si>
+  <si>
+    <t>joystick</t>
+  </si>
+  <si>
+    <t>Coupling equipment for snake mode</t>
+  </si>
+  <si>
+    <t>Coupling equipment for skid-steer mode</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Instrument Build</t>
+  </si>
+  <si>
+    <t>The cost information contained in this document is of a budgetary and planning nature and is intended for informational purposes only.  It does not constitute a commitment on the part of Rice University or Lamont-Doherty Earth Observatory.</t>
+  </si>
+  <si>
+    <t>E8</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
+  <si>
+    <t>E12</t>
+  </si>
+  <si>
+    <t>E13</t>
+  </si>
+  <si>
+    <t>Instruments</t>
+  </si>
+  <si>
+    <t>Mechanical system</t>
+  </si>
+  <si>
+    <t>Electronical system</t>
+  </si>
+  <si>
+    <t>Tools</t>
+  </si>
+  <si>
+    <t>https://www.sparkfun.com/sparkfun-gps-rtk-sma-breakout-zed-f9p-qwiic.html?gad_source=1&amp;gad_campaignid=17479024030&amp;gbraid=0AAAAADsj4ESZo4z6J-lZi4oH-Gbee1tDp&amp;gclid=CjwKCAjwpOfHBhAxEiwAm1SwEhJyyYfaN2KHVCNsFHo5kOdAcR0OF-yeA8rnDiwfwkZM3xz7EArGcxoCTRwQAvD_BwE</t>
+  </si>
+  <si>
+    <t>Open Log Artemis</t>
+  </si>
+  <si>
+    <t>E14</t>
+  </si>
+  <si>
+    <t>sparfun</t>
+  </si>
+  <si>
+    <t>CjwKCAjwpOfHBhAxEiwAm1SwEgGs8VFxhSpFGDrF6AeHjYDrzAfPAl0BzaCyyi5uLWIJA0sdUTnuBRoCKWYQAvD_BwE</t>
+  </si>
+  <si>
+    <t>GNSS caxial antenna cable and antenna</t>
+  </si>
+  <si>
+    <t>https://www.sparkfun.com/gnss-multi-band-magnetic-mount-antenna-5m-sma.html?gad_source=1&amp;gad_campaignid=17479024030&amp;gbraid=0AAAAADsj4ESZo4z6J-lZi4oH-Gbee1tDp&amp;gclid=CjwKCAjwpOfHBhAxEiwAm1SwEm2hcZXjJ74rWbhTVg4Vf5_kyIM-BRwpnGG_LwPhgWzQJsawM5TUghoCaXMQAvD_BwE</t>
+  </si>
+  <si>
+    <t>© 2022 University of Washington. Quaternary Research Center sponsorship acknowledged</t>
+  </si>
+  <si>
+    <t>Waveshare</t>
+  </si>
+  <si>
+    <t>waveshare</t>
+  </si>
+  <si>
+    <t>https://www.waveshare.com/d200-lidar-kit.htm?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>https://www.waveshare.com/oak-d-pro.htm?utm_source=chatgpt.com</t>
   </si>
 </sst>
 </file>
@@ -325,7 +429,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -348,6 +452,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -357,12 +469,65 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -373,7 +538,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -383,8 +548,16 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -404,9 +577,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -444,9 +617,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -479,26 +652,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -531,26 +687,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -724,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.6640625" customWidth="1"/>
@@ -739,24 +878,24 @@
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>60</v>
+        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="K2" s="3">
-        <f>SUM(J5:J120)</f>
-        <v>309.67</v>
+        <f>SUM(J5:J123)</f>
+        <v>260781.6</v>
       </c>
     </row>
     <row r="3" spans="1:11" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>61</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4" spans="1:11" s="4" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
@@ -795,100 +934,90 @@
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="A5" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="9"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" t="s">
         <v>74</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>86.95</v>
-      </c>
-      <c r="J5" s="1">
-        <v>86.95</v>
-      </c>
-      <c r="K5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>65</v>
+        <v>98</v>
       </c>
       <c r="F6">
         <v>1</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I6" s="1">
-        <v>25.18</v>
-      </c>
-      <c r="J6" s="1">
-        <f>I6*H6</f>
-        <v>75.539999999999992</v>
+        <v>43495</v>
+      </c>
+      <c r="J6" s="7">
+        <f t="shared" ref="J6" si="0">I6*H6</f>
+        <v>86990</v>
       </c>
       <c r="K6" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H7">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="I7" s="1">
+        <v>2995</v>
+      </c>
+      <c r="J7" s="7">
+        <f t="shared" ref="J7:J13" si="1">I7*H7</f>
+        <v>5990</v>
       </c>
       <c r="K7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
@@ -896,401 +1025,902 @@
         <v>75</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
+        <v>77</v>
+      </c>
+      <c r="D8" t="s">
+        <v>60</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8" s="1">
+        <v>3295</v>
+      </c>
+      <c r="J8" s="7">
+        <f t="shared" si="1"/>
+        <v>6590</v>
+      </c>
+      <c r="K8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B9" t="s">
+        <v>102</v>
+      </c>
+      <c r="C9" t="s">
         <v>77</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="6">
-        <v>1</v>
-      </c>
-      <c r="G9" s="6">
-        <v>4</v>
-      </c>
-      <c r="H9" s="6">
-        <v>4</v>
-      </c>
-      <c r="I9" s="8">
-        <v>24.99</v>
-      </c>
-      <c r="J9" s="8">
-        <f>I9*H9</f>
-        <v>99.96</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="D9" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="6">
-        <v>1</v>
-      </c>
-      <c r="G11" s="6">
-        <v>1</v>
-      </c>
-      <c r="H11" s="6">
-        <v>1</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" t="s">
+        <v>60</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="9"/>
+      <c r="I11" s="9"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D12" t="s">
+        <v>60</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13">
+        <v>6</v>
+      </c>
+      <c r="I13" s="1">
+        <v>4695</v>
+      </c>
+      <c r="J13" s="7">
+        <f t="shared" si="1"/>
+        <v>28170</v>
+      </c>
+      <c r="K13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" s="1">
+        <v>249</v>
+      </c>
+      <c r="J14" s="7">
+        <f>I14*H14</f>
+        <v>498</v>
+      </c>
+      <c r="K14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
         <v>81</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16">
+        <v>6</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="J16" s="7"/>
+      <c r="K16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" t="s">
         <v>83</v>
       </c>
-      <c r="F12" s="6">
-        <v>1</v>
-      </c>
-      <c r="G12" s="6">
-        <v>1</v>
-      </c>
-      <c r="H12" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="C17" t="s">
         <v>87</v>
       </c>
-      <c r="B13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="D17" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>2</v>
+      </c>
+      <c r="I17" s="1">
+        <v>18.989999999999998</v>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C18" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="6">
-        <v>1</v>
-      </c>
-      <c r="G13" s="6">
-        <v>1</v>
-      </c>
-      <c r="H13" s="6">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="D18" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" t="s">
-        <v>90</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
+      <c r="F18">
+        <v>3</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" s="1">
+        <v>13.49</v>
+      </c>
+      <c r="J18" s="7"/>
+      <c r="K18" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
       </c>
       <c r="D19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19" s="1">
+        <v>59.95</v>
+      </c>
+      <c r="J19" s="7">
+        <f>H19*I19</f>
+        <v>119.9</v>
+      </c>
+      <c r="K19" t="s">
         <v>15</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19">
-        <v>1</v>
-      </c>
-      <c r="I19" s="1">
-        <v>13.24</v>
-      </c>
-      <c r="J19" s="1">
-        <v>13.24</v>
-      </c>
-      <c r="K19" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="B20" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20">
-        <v>585006</v>
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="F20">
         <v>1</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20">
-        <v>2</v>
-      </c>
-      <c r="I20" s="1">
-        <v>16.989999999999998</v>
-      </c>
-      <c r="J20" s="1">
-        <v>33.979999999999997</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="J20" s="7"/>
       <c r="K20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E21" s="5"/>
+      <c r="A21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E22" s="5"/>
+      <c r="A22" t="s">
+        <v>56</v>
+      </c>
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="J22" s="7"/>
+      <c r="K22" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E23" s="5"/>
+      <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="J23" s="7"/>
+      <c r="K23" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="E24" s="5"/>
+      <c r="A24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C24" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="J24" s="7"/>
+      <c r="K24" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="6"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-      <c r="H25" s="6"/>
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
+        <v>118</v>
+      </c>
+      <c r="C25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25" s="1">
+        <v>13.24</v>
+      </c>
+      <c r="J25" s="7">
+        <v>13.24</v>
+      </c>
+      <c r="K25" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" t="s">
-        <v>35</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="K26" t="s">
-        <v>36</v>
-      </c>
+      <c r="A26" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
+        <v>69</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="D27" t="s">
+        <v>125</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F27" s="16">
+        <v>1</v>
+      </c>
+      <c r="G27" s="16">
+        <v>2</v>
+      </c>
+      <c r="H27" s="16">
+        <v>2</v>
+      </c>
+      <c r="I27" s="1">
+        <v>399.99</v>
+      </c>
+      <c r="J27" s="7">
+        <f>H27*I27</f>
+        <v>799.98</v>
       </c>
       <c r="K27" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" t="s">
+        <v>124</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
       </c>
       <c r="G28">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="H28">
+        <v>2</v>
+      </c>
+      <c r="I28" s="1">
+        <v>54.99</v>
+      </c>
+      <c r="J28" s="7">
+        <f>H28*I28</f>
+        <v>109.98</v>
       </c>
       <c r="K28" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>95</v>
+      </c>
+      <c r="C29" t="s">
+        <v>53</v>
+      </c>
+      <c r="D29" t="s">
+        <v>97</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29" s="1">
+        <v>259.95</v>
+      </c>
+      <c r="J29" s="7">
+        <f>H29*I29</f>
+        <v>779.84999999999991</v>
       </c>
       <c r="K29" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>44</v>
+        <v>121</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>96</v>
+      </c>
+      <c r="C30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" t="s">
+        <v>97</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="H30">
+        <v>3</v>
+      </c>
+      <c r="I30" s="1">
+        <v>109.95</v>
+      </c>
+      <c r="J30" s="7">
+        <f>I30*H30</f>
+        <v>329.85</v>
       </c>
       <c r="K30" t="s">
-        <v>13</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>46</v>
-      </c>
-      <c r="B31" t="s">
-        <v>47</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="K31" t="s">
-        <v>48</v>
-      </c>
+      <c r="A31" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="9"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="G32">
         <v>1</v>
       </c>
+      <c r="J32" s="7"/>
       <c r="K32" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="G33">
         <v>1</v>
       </c>
+      <c r="J33" s="7"/>
       <c r="K33" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="G34">
         <v>1</v>
       </c>
+      <c r="J34" s="7"/>
       <c r="K34" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
       <c r="G35">
         <v>1</v>
       </c>
+      <c r="J35" s="7"/>
       <c r="K35" t="s">
-        <v>23</v>
-      </c>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="J36" s="7"/>
+      <c r="K36" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="G37">
+        <v>1</v>
+      </c>
+      <c r="J37" s="7"/>
+      <c r="K37" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>42</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="J38" s="7"/>
+      <c r="K38" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="J39" s="7"/>
+      <c r="K39" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="G40">
+        <v>1</v>
+      </c>
+      <c r="J40" s="7"/>
+      <c r="K40" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" t="s">
+        <v>51</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="J41" s="7"/>
+      <c r="K41" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="J42" s="14">
+        <f>SUM(J6:J41)</f>
+        <v>130390.8</v>
+      </c>
+      <c r="K42" s="15"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:K4" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -1299,8 +1929,8 @@
     </sortState>
   </autoFilter>
   <hyperlinks>
-    <hyperlink ref="E19" r:id="rId1" xr:uid="{02A1447F-14E3-2B4D-880B-2FA468205AEF}"/>
-    <hyperlink ref="E20" r:id="rId2" xr:uid="{A6F3A764-BA5E-A74E-A658-CD66001C85F5}"/>
+    <hyperlink ref="E25" r:id="rId1" xr:uid="{02A1447F-14E3-2B4D-880B-2FA468205AEF}"/>
+    <hyperlink ref="E15" r:id="rId2" xr:uid="{469FFF1E-34FA-E04E-8B47-70D39F820D67}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
